--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Síntese" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Série histórica 2013-2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Premissas macro 2026-2033" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PIB projetado" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Projeção IBS 2029-2033" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntese" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Série histórica 2013-2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premissas macro 2026-2033" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB projetado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projeção IBS 2029-2033" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>IBS bruto nacional: de R$ 109.7 bi em 2029 a R$ 1,194.4 bi em 2033 (R$ constantes de 2025).</t>
+          <t>IBS bruto nacional: de R$ 110.0 bi em 2029 a R$ 1,198.1 bi em 2033 (R$ constantes de 2025).</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>R$ 1,194.4 bi (7.99% do PIB, a mesma proporção de 2025, por premissa)</t>
+          <t>R$ 1,198.1 bi (8.02% do PIB, a mesma proporção de 2025, por premissa)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1047,14 +1047,14 @@
         <v>72575738376.57001</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>11699003388.68</v>
+        <v>13510645883.15</v>
       </c>
       <c r="E11" s="9">
         <f>B11+C11+D11</f>
         <v/>
       </c>
       <c r="F11" s="8" t="n">
-        <v>812449707692.41</v>
+        <v>814970657770.4</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>7389130999453.28</v>
@@ -1080,14 +1080,14 @@
         <v>72939656553.14</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>12775546215.27</v>
+        <v>14626111775.69</v>
       </c>
       <c r="E12" s="9">
         <f>B12+C12+D12</f>
         <v/>
       </c>
       <c r="F12" s="8" t="n">
-        <v>794035846100.87</v>
+        <v>796499659810.45</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>7609597000575.82</v>
@@ -1113,14 +1113,14 @@
         <v>90315695421.34</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>15797405283.66</v>
+        <v>18121397167.85</v>
       </c>
       <c r="E13" s="9">
         <f>B13+C13+D13</f>
         <v/>
       </c>
       <c r="F13" s="8" t="n">
-        <v>906017464408.6801</v>
+        <v>908828745865.16</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>9012141999284.48</v>
@@ -1146,14 +1146,14 @@
         <v>105738689405.94</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>14732300782.29</v>
+        <v>17215116819.65</v>
       </c>
       <c r="E14" s="9">
         <f>B14+C14+D14</f>
         <v/>
       </c>
       <c r="F14" s="8" t="n">
-        <v>915004147351.87</v>
+        <v>917843313585.53</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>10079676679176</v>
@@ -1179,14 +1179,14 @@
         <v>120982841687.58</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>12037722674.32</v>
+        <v>14594149274.45</v>
       </c>
       <c r="E15" s="9">
         <f>B15+C15+D15</f>
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>900518229101.66</v>
+        <v>903312446981.72</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>10943344667905</v>
@@ -1212,14 +1212,14 @@
         <v>139810741117.97</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>13618393510.28</v>
+        <v>16560156010.15</v>
       </c>
       <c r="E16" s="9">
         <f>B16+C16+D16</f>
         <v/>
       </c>
       <c r="F16" s="8" t="n">
-        <v>988498089486.5</v>
+        <v>991565300062.34</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>11779250581628.3</v>
@@ -1245,14 +1245,14 @@
         <v>153789986855.54</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>13981757501.54</v>
+        <v>17136685627.32</v>
       </c>
       <c r="E17" s="9">
         <f>B17+C17+D17</f>
         <v/>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1016767628985.46</v>
+        <v>1019922557111.24</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>12738565613881.1</v>
@@ -1764,7 +1764,7 @@
         <v>2026</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1033149971592.79</v>
+        <v>1036411135097.23</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>12991145892873.13</v>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
